--- a/Field/templates/template_gimokji.xlsx
+++ b/Field/templates/template_gimokji.xlsx
@@ -19037,9 +19037,8 @@
           <t>Ds:</t>
         </is>
       </c>
-      <c r="P5" s="1131">
-        <f>IF(입력!E16=0,입력!D16,2*(입력!E16*입력!F16)/(입력!E16+입력!F16))</f>
-        <v/>
+      <c r="P5" s="1131" t="n">
+        <v>0.8000000000000002</v>
       </c>
       <c r="Q5" s="1829" t="n"/>
       <c r="R5" s="230" t="inlineStr">
@@ -19052,9 +19051,8 @@
           <t>A:</t>
         </is>
       </c>
-      <c r="T5" s="1832">
-        <f>IF(입력!$E$16=0,I13*I13*PI()/4,입력!$E$16*입력!$F$16)</f>
-        <v/>
+      <c r="T5" s="1832" t="n">
+        <v>0.6400000000000001</v>
       </c>
       <c r="U5" s="1829" t="n"/>
       <c r="V5" s="232" t="inlineStr">
@@ -19071,9 +19069,8 @@
       <c r="Y5" s="1829" t="n"/>
       <c r="Z5" s="1829" t="n"/>
       <c r="AA5" s="1830" t="n"/>
-      <c r="AB5" s="1828">
-        <f>'먼지측정 사전 Data'!H62</f>
-        <v/>
+      <c r="AB5" s="1828" t="n">
+        <v>0.84</v>
       </c>
       <c r="AC5" s="1829" t="n"/>
       <c r="AD5" s="1829" t="n"/>
@@ -19204,9 +19201,8 @@
       <c r="Y8" s="1837" t="n"/>
       <c r="Z8" s="1837" t="n"/>
       <c r="AA8" s="1838" t="n"/>
-      <c r="AB8" s="1828">
-        <f>'먼지측정 사전 Data'!H11</f>
-        <v/>
+      <c r="AB8" s="1828" t="n">
+        <v>751.7</v>
       </c>
       <c r="AC8" s="1837" t="n"/>
       <c r="AD8" s="1837" t="n"/>
@@ -19324,27 +19320,24 @@
           <t>1번:</t>
         </is>
       </c>
-      <c r="P11" s="1030">
-        <f>P5/2</f>
-        <v/>
+      <c r="P11" s="1030" t="n">
+        <v>0.4000000000000001</v>
       </c>
       <c r="R11" s="1031" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="S11" s="1031">
-        <f>IF(입력!D16&lt;1,0.707,0.5)</f>
-        <v/>
+      <c r="S11" s="1031" t="n">
+        <v>0.707</v>
       </c>
       <c r="U11" s="237" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="V11" s="1847">
-        <f>P11*S11</f>
-        <v/>
+      <c r="V11" s="1847" t="n">
+        <v>0.2828000000000001</v>
       </c>
       <c r="W11" s="1831" t="inlineStr">
         <is>
@@ -19381,32 +19374,14 @@
       <c r="L12" s="1829" t="n"/>
       <c r="M12" s="1829" t="n"/>
       <c r="N12" s="1829" t="n"/>
-      <c r="O12" s="238">
-        <f>IF(입력!D16&lt;1,"","2번")</f>
-        <v/>
-      </c>
-      <c r="P12" s="1135">
-        <f>IF(O12="","",0.75)</f>
-        <v/>
-      </c>
+      <c r="O12" s="238" t="str"/>
+      <c r="P12" s="1135" t="str"/>
       <c r="Q12" s="1827" t="n"/>
-      <c r="R12" s="1136">
-        <f>IF(P12="","",R11)</f>
-        <v/>
-      </c>
-      <c r="S12" s="1136">
-        <f>IF(R12="","",0.866)</f>
-        <v/>
-      </c>
+      <c r="R12" s="1136" t="str"/>
+      <c r="S12" s="1136" t="str"/>
       <c r="T12" s="1827" t="n"/>
-      <c r="U12" s="240">
-        <f>IF(S12="","","=")</f>
-        <v/>
-      </c>
-      <c r="V12" s="1848">
-        <f>IF(U12="","",P12*S12)</f>
-        <v/>
-      </c>
+      <c r="U12" s="240" t="str"/>
+      <c r="V12" s="1848" t="str"/>
       <c r="W12" s="1831" t="inlineStr">
         <is>
           <t>흡인노즐 직경, cm:</t>
@@ -19810,9 +19785,10 @@
       <c r="AO20" s="13" t="n"/>
     </row>
     <row r="21" ht="24.6" customFormat="1" customHeight="1" s="2">
-      <c r="A21" s="1856">
-        <f>'먼지측정 사전 Data'!H64</f>
-        <v/>
+      <c r="A21" s="1856" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
       </c>
       <c r="B21" s="1837" t="n"/>
       <c r="C21" s="1838" t="n"/>
@@ -20210,9 +20186,8 @@
       </c>
       <c r="Q31" s="1829" t="n"/>
       <c r="R31" s="1830" t="n"/>
-      <c r="S31" s="1859">
-        <f>SUM(S21:U30)</f>
-        <v/>
+      <c r="S31" s="1859" t="n">
+        <v>0.4019</v>
       </c>
       <c r="T31" s="1829" t="n"/>
       <c r="U31" s="1830" t="n"/>
@@ -20252,9 +20227,8 @@
       <c r="D32" s="1829" t="n"/>
       <c r="E32" s="1829" t="n"/>
       <c r="F32" s="1830" t="n"/>
-      <c r="G32" s="1857">
-        <f>G21</f>
-        <v/>
+      <c r="G32" s="1857" t="n">
+        <v>9.750801878999999</v>
       </c>
       <c r="H32" s="1829" t="n"/>
       <c r="I32" s="1830" t="n"/>
@@ -20287,9 +20261,8 @@
       <c r="AB32" s="1856" t="n"/>
       <c r="AC32" s="1829" t="n"/>
       <c r="AD32" s="1830" t="n"/>
-      <c r="AE32" s="1856">
-        <f>'먼지측정 사전 Data'!R86</f>
-        <v/>
+      <c r="AE32" s="1856" t="n">
+        <v>16</v>
       </c>
       <c r="AF32" s="1829" t="n"/>
       <c r="AG32" s="1830" t="n"/>
@@ -20405,9 +20378,10 @@
           <t>업   소   명:</t>
         </is>
       </c>
-      <c r="W51" s="1125">
-        <f>I5</f>
-        <v/>
+      <c r="W51" s="1125" t="inlineStr">
+        <is>
+          <t>대한자동차1급공업사</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="730">
@@ -20513,9 +20487,8 @@
           <t>=</t>
         </is>
       </c>
-      <c r="R55" s="1864">
-        <f>'먼지측정 사전 Data'!H56</f>
-        <v/>
+      <c r="R55" s="1864" t="n">
+        <v>1.986317872332676</v>
       </c>
       <c r="V55" s="14" t="inlineStr">
         <is>
@@ -20533,9 +20506,8 @@
       </c>
       <c r="W56" s="1827" t="n"/>
       <c r="X56" s="1827" t="n"/>
-      <c r="Y56" s="1060">
-        <f>'먼지측정 사전 Data'!H48</f>
-        <v/>
+      <c r="Y56" s="1060" t="n">
+        <v>0.1499999999999773</v>
       </c>
       <c r="AG56" s="205" t="n"/>
     </row>
@@ -20581,9 +20553,8 @@
       <c r="A59" s="204" t="n"/>
       <c r="M59" s="205" t="n"/>
       <c r="N59" s="204" t="n"/>
-      <c r="P59" s="1026">
-        <f>'먼지측정 사전 Data'!H55</f>
-        <v/>
+      <c r="P59" s="1026" t="n">
+        <v>10.2</v>
       </c>
       <c r="R59" s="1055" t="inlineStr">
         <is>
@@ -20601,9 +20572,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="X59" s="1026">
-        <f>'먼지측정 사전 Data'!H11</f>
-        <v/>
+      <c r="X59" s="1026" t="n">
+        <v>751.7</v>
       </c>
       <c r="Y59" s="1827" t="n"/>
       <c r="Z59" s="17" t="inlineStr">
@@ -20611,9 +20581,8 @@
           <t>+</t>
         </is>
       </c>
-      <c r="AA59" s="1866">
-        <f>'먼지측정 사전 Data'!O52</f>
-        <v/>
+      <c r="AA59" s="1866" t="n">
+        <v>3.74</v>
       </c>
       <c r="AB59" s="1827" t="n"/>
       <c r="AC59" s="1026" t="inlineStr">
@@ -20625,14 +20594,12 @@
         <v>22.4</v>
       </c>
       <c r="AE59" s="1827" t="n"/>
-      <c r="AF59" s="1075">
-        <f>Y56</f>
-        <v/>
+      <c r="AF59" s="1075" t="n">
+        <v>0.1499999999999773</v>
       </c>
       <c r="AG59" s="1854" t="n"/>
-      <c r="AK59" s="1867">
-        <f>AA59</f>
-        <v/>
+      <c r="AK59" s="1867" t="n">
+        <v>3.74</v>
       </c>
     </row>
     <row r="60" ht="14.1" customFormat="1" customHeight="1" s="14">
@@ -20660,9 +20627,8 @@
         </is>
       </c>
       <c r="T60" s="17" t="n"/>
-      <c r="U60" s="1026">
-        <f>'먼지측정 사전 Data'!H51</f>
-        <v/>
+      <c r="U60" s="1026" t="n">
+        <v>27.5</v>
       </c>
       <c r="V60" s="1827" t="n"/>
       <c r="W60" s="1827" t="n"/>
@@ -20733,9 +20699,8 @@
           <t>=</t>
         </is>
       </c>
-      <c r="T62" s="1864">
-        <f>'먼지측정 사전 Data'!R78</f>
-        <v/>
+      <c r="T62" s="1864" t="n">
+        <v>1.173132428657962</v>
       </c>
       <c r="X62" s="1114" t="inlineStr">
         <is>
@@ -20743,9 +20708,8 @@
         </is>
       </c>
       <c r="AG62" s="205" t="n"/>
-      <c r="AK62" s="1868">
-        <f>T62</f>
-        <v/>
+      <c r="AK62" s="1868" t="n">
+        <v>1.173132428657962</v>
       </c>
     </row>
     <row r="63" ht="14.1" customFormat="1" customHeight="1" s="14">
@@ -20778,9 +20742,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="W64" s="1026">
-        <f>'먼지측정 사전 Data'!H11</f>
-        <v/>
+      <c r="W64" s="1026" t="n">
+        <v>751.7</v>
       </c>
       <c r="X64" s="1827" t="n"/>
       <c r="Y64" s="17" t="inlineStr">
@@ -20788,15 +20751,13 @@
           <t>+</t>
         </is>
       </c>
-      <c r="Z64" s="1026">
-        <f>('먼지측정 사전 Data'!R68)/13.6</f>
-        <v/>
+      <c r="Z64" s="1026" t="n">
+        <v>-0.5514705882352942</v>
       </c>
       <c r="AA64" s="1827" t="n"/>
       <c r="AG64" s="205" t="n"/>
-      <c r="AK64" s="1867">
-        <f>Z64</f>
-        <v/>
+      <c r="AK64" s="1867" t="n">
+        <v>-0.5514705882352942</v>
       </c>
       <c r="AL64" s="484" t="n"/>
     </row>
@@ -20809,9 +20770,8 @@
           <t>273+</t>
         </is>
       </c>
-      <c r="T65" s="1061">
-        <f>'먼지측정 사전 Data'!R66</f>
-        <v/>
+      <c r="T65" s="1061" t="n">
+        <v>26</v>
       </c>
       <c r="W65" s="1076" t="n">
         <v>760</v>
@@ -20909,9 +20869,8 @@
           <t>=</t>
         </is>
       </c>
-      <c r="T68" s="1864">
-        <f>'먼지측정 사전 Data'!H62*SQRT((2*9.81*'먼지측정 사전 Data'!R67)/'먼지측정 사전 Data'!R78)</f>
-        <v/>
+      <c r="T68" s="1864" t="n">
+        <v>10.19052605274819</v>
       </c>
       <c r="X68" s="14" t="inlineStr">
         <is>
@@ -20919,9 +20878,8 @@
         </is>
       </c>
       <c r="AG68" s="205" t="n"/>
-      <c r="AK68" s="1868">
-        <f>T68</f>
-        <v/>
+      <c r="AK68" s="1868" t="n">
+        <v>10.19052605274819</v>
       </c>
     </row>
     <row r="69" ht="6" customFormat="1" customHeight="1" s="14" thickBot="1">
@@ -20944,9 +20902,8 @@
           <t>v=</t>
         </is>
       </c>
-      <c r="P70" s="1061">
-        <f>'먼지측정 사전 Data'!H62</f>
-        <v/>
+      <c r="P70" s="1061" t="n">
+        <v>0.84</v>
       </c>
       <c r="R70" s="1054" t="inlineStr">
         <is>
@@ -20960,9 +20917,8 @@
       </c>
       <c r="T70" s="213" t="n"/>
       <c r="U70" s="213" t="n"/>
-      <c r="V70" s="1112">
-        <f>'먼지측정 사전 Data'!R67</f>
-        <v/>
+      <c r="V70" s="1112" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="W70" s="1869" t="n"/>
       <c r="X70" s="1869" t="n"/>
@@ -20972,9 +20928,8 @@
       <c r="A71" s="204" t="n"/>
       <c r="M71" s="205" t="n"/>
       <c r="N71" s="1865" t="n"/>
-      <c r="S71" s="1870">
-        <f>'먼지측정 사전 Data'!R78</f>
-        <v/>
+      <c r="S71" s="1870" t="n">
+        <v>1.173132428657962</v>
       </c>
       <c r="AG71" s="205" t="n"/>
     </row>
@@ -21032,9 +20987,8 @@
           <t>=</t>
         </is>
       </c>
-      <c r="AB74" s="1864">
-        <f>'먼지측정 사전 Data'!R80</f>
-        <v/>
+      <c r="AB74" s="1864" t="n">
+        <v>6.544922952928824</v>
       </c>
       <c r="AF74" s="14" t="inlineStr">
         <is>
@@ -21057,18 +21011,16 @@
           <t>Vic=</t>
         </is>
       </c>
-      <c r="P76" s="1871">
-        <f>S31*1000</f>
-        <v/>
+      <c r="P76" s="1871" t="n">
+        <v>401.9</v>
       </c>
       <c r="S76" s="1055" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="T76" s="1871">
-        <f>R55</f>
-        <v/>
+      <c r="T76" s="1871" t="n">
+        <v>1.986317872332676</v>
       </c>
       <c r="U76" s="1827" t="n"/>
       <c r="V76" s="1827" t="n"/>
@@ -21111,9 +21063,8 @@
         </is>
       </c>
       <c r="U77" s="1829" t="n"/>
-      <c r="V77" s="1872">
-        <f>R55</f>
-        <v/>
+      <c r="V77" s="1872" t="n">
+        <v>1.986317872332676</v>
       </c>
       <c r="W77" s="1829" t="n"/>
       <c r="X77" s="1829" t="n"/>
@@ -21244,9 +21195,8 @@
           <t>=</t>
         </is>
       </c>
-      <c r="M85" s="1873">
-        <f>(E87*(0.00346*K87+N87/Q87*(T87+W87/13.6)))/(I88*M88*Q88*U88)*1.667*10^4</f>
-        <v/>
+      <c r="M85" s="1873" t="n">
+        <v>99.32224627337398</v>
       </c>
       <c r="N85" s="1837" t="n"/>
       <c r="O85" s="1837" t="n"/>
@@ -21272,9 +21222,8 @@
       <c r="AE85" s="1066" t="n"/>
       <c r="AF85" s="1066" t="n"/>
       <c r="AG85" s="243" t="n"/>
-      <c r="AK85" s="1874">
-        <f>M85</f>
-        <v/>
+      <c r="AK85" s="1874" t="n">
+        <v>99.32224627337398</v>
       </c>
     </row>
     <row r="86" ht="24.6" customHeight="1" s="730">
@@ -21288,9 +21237,8 @@
           <t>I(%)=</t>
         </is>
       </c>
-      <c r="E87" s="1032">
-        <f>('먼지측정 사전 Data'!R66)+273</f>
-        <v/>
+      <c r="E87" s="1032" t="n">
+        <v>299</v>
       </c>
       <c r="F87" s="1827" t="n"/>
       <c r="G87" s="1165" t="inlineStr">
@@ -21301,9 +21249,8 @@
       <c r="H87" s="1165" t="n"/>
       <c r="I87" s="1165" t="n"/>
       <c r="J87" s="1165" t="n"/>
-      <c r="K87" s="1875">
-        <f>'먼지측정 사전 Data'!H80</f>
-        <v/>
+      <c r="K87" s="1875" t="n">
+        <v>6.544922952928824</v>
       </c>
       <c r="L87" s="1827" t="n"/>
       <c r="M87" s="1165" t="inlineStr">
@@ -21311,9 +21258,8 @@
           <t>+</t>
         </is>
       </c>
-      <c r="N87" s="1032">
-        <f>'먼지측정 사전 Data'!H77</f>
-        <v/>
+      <c r="N87" s="1032" t="n">
+        <v>0.4019</v>
       </c>
       <c r="O87" s="1827" t="n"/>
       <c r="P87" s="214" t="inlineStr">
@@ -21321,9 +21267,8 @@
           <t>/</t>
         </is>
       </c>
-      <c r="Q87" s="1032">
-        <f>('먼지측정 사전 Data'!R71)+273</f>
-        <v/>
+      <c r="Q87" s="1032" t="n">
+        <v>300.5</v>
       </c>
       <c r="R87" s="1827" t="n"/>
       <c r="S87" s="1165" t="inlineStr">
@@ -21331,9 +21276,8 @@
           <t>(</t>
         </is>
       </c>
-      <c r="T87" s="1032">
-        <f>'먼지측정 사전 Data'!H11</f>
-        <v/>
+      <c r="T87" s="1032" t="n">
+        <v>751.7</v>
       </c>
       <c r="U87" s="1827" t="n"/>
       <c r="V87" s="1165" t="inlineStr">
@@ -21341,9 +21285,8 @@
           <t>+</t>
         </is>
       </c>
-      <c r="W87" s="1876">
-        <f>'먼지측정 사전 Data'!H83</f>
-        <v/>
+      <c r="W87" s="1876" t="n">
+        <v>29.79412960356355</v>
       </c>
       <c r="X87" s="1827" t="n"/>
       <c r="Y87" s="214" t="inlineStr">
@@ -21368,9 +21311,8 @@
         </is>
       </c>
       <c r="AG87" s="1854" t="n"/>
-      <c r="AK87" s="1877">
-        <f>W87</f>
-        <v/>
+      <c r="AK87" s="1877" t="n">
+        <v>29.79412960356355</v>
       </c>
     </row>
     <row r="88" ht="24.6" customHeight="1" s="730">
@@ -21382,9 +21324,8 @@
       <c r="F88" s="1165" t="n"/>
       <c r="G88" s="1165" t="n"/>
       <c r="H88" s="1165" t="n"/>
-      <c r="I88" s="1878">
-        <f>760+(('먼지측정 사전 Data'!H68)/13.6)</f>
-        <v/>
+      <c r="I88" s="1878" t="n">
+        <v>759.4485294117648</v>
       </c>
       <c r="J88" s="1829" t="n"/>
       <c r="K88" s="1829" t="n"/>
@@ -21393,9 +21334,8 @@
           <t>·</t>
         </is>
       </c>
-      <c r="M88" s="1088">
-        <f>'먼지측정 사전 Data'!H72</f>
-        <v/>
+      <c r="M88" s="1088" t="n">
+        <v>22</v>
       </c>
       <c r="N88" s="1829" t="n"/>
       <c r="O88" s="1829" t="n"/>
@@ -21404,9 +21344,8 @@
           <t>·</t>
         </is>
       </c>
-      <c r="Q88" s="1879">
-        <f>'먼지측정 사전 Data'!H79</f>
-        <v/>
+      <c r="Q88" s="1879" t="n">
+        <v>10.19052605274819</v>
       </c>
       <c r="R88" s="1829" t="n"/>
       <c r="S88" s="1829" t="n"/>
@@ -21415,9 +21354,8 @@
           <t>·</t>
         </is>
       </c>
-      <c r="U88" s="1089">
-        <f>PI()*('먼지측정 사전 Data'!H81)^2/4</f>
-        <v/>
+      <c r="U88" s="1089" t="n">
+        <v>0.3038579830478584</v>
       </c>
       <c r="V88" s="1829" t="n"/>
       <c r="W88" s="1829" t="n"/>
@@ -22116,9 +22054,8 @@
           <t>배출가스량 계산 =</t>
         </is>
       </c>
-      <c r="J109" s="1883">
-        <f>F111*K111*O111/(273+Q112)*(T111+W111)/T112*(1-(AB111/AB112))*AF111</f>
-        <v/>
+      <c r="J109" s="1883" t="n">
+        <v>20766.79477132404</v>
       </c>
       <c r="O109" s="1064" t="inlineStr">
         <is>
@@ -22131,9 +22068,8 @@
         </is>
       </c>
       <c r="S109" s="1837" t="n"/>
-      <c r="T109" s="1884">
-        <f>J109/60</f>
-        <v/>
+      <c r="T109" s="1884" t="n">
+        <v>346.113246188734</v>
       </c>
       <c r="U109" s="1837" t="n"/>
       <c r="V109" s="1837" t="n"/>
@@ -22160,9 +22096,8 @@
           <t>(</t>
         </is>
       </c>
-      <c r="F111" s="1885">
-        <f>'먼지측정 사전 Data'!H79</f>
-        <v/>
+      <c r="F111" s="1885" t="n">
+        <v>10.19052605274819</v>
       </c>
       <c r="H111" s="807" t="inlineStr">
         <is>
@@ -22179,9 +22114,8 @@
           <t>(</t>
         </is>
       </c>
-      <c r="K111" s="1886">
-        <f>AB14</f>
-        <v/>
+      <c r="K111" s="1886" t="n">
+        <v>0.6400000000000001</v>
       </c>
       <c r="M111" s="807" t="inlineStr">
         <is>
@@ -22204,9 +22138,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="T111" s="1032">
-        <f>'먼지측정 사전 Data'!H11</f>
-        <v/>
+      <c r="T111" s="1032" t="n">
+        <v>751.7</v>
       </c>
       <c r="U111" s="1827" t="n"/>
       <c r="V111" s="1165" t="inlineStr">
@@ -22214,9 +22147,8 @@
           <t>+</t>
         </is>
       </c>
-      <c r="W111" s="1887">
-        <f>('먼지측정 사전 Data'!H68)/13.6</f>
-        <v/>
+      <c r="W111" s="1887" t="n">
+        <v>-0.5514705882352942</v>
       </c>
       <c r="X111" s="1827" t="n"/>
       <c r="Y111" s="1024" t="inlineStr">
@@ -22234,9 +22166,8 @@
           <t>1-</t>
         </is>
       </c>
-      <c r="AB111" s="1888">
-        <f>'먼지측정 사전 Data'!H56</f>
-        <v/>
+      <c r="AB111" s="1888" t="n">
+        <v>1.986317872332676</v>
       </c>
       <c r="AC111" s="1827" t="n"/>
       <c r="AD111" s="807" t="inlineStr">
@@ -22261,9 +22192,8 @@
           <t>273+</t>
         </is>
       </c>
-      <c r="Q112" s="1100">
-        <f>'먼지측정 사전 Data'!R66</f>
-        <v/>
+      <c r="Q112" s="1100" t="n">
+        <v>26</v>
       </c>
       <c r="R112" s="1837" t="n"/>
       <c r="T112" s="807" t="n">
@@ -22391,9 +22321,8 @@
       <c r="G121" s="1837" t="n"/>
       <c r="H121" s="1837" t="n"/>
       <c r="I121" s="1837" t="n"/>
-      <c r="J121" s="1889">
-        <f>ROUND(L124*(273+M126)*Q126/(F125*K125*(Q125+U125/13.6)),1)</f>
-        <v/>
+      <c r="J121" s="1889" t="n">
+        <v>0</v>
       </c>
       <c r="K121" s="1837" t="n"/>
       <c r="L121" s="1837" t="n"/>
@@ -22405,9 +22334,8 @@
         </is>
       </c>
       <c r="AG121" s="248" t="n"/>
-      <c r="AK121" s="1161">
-        <f>L124*((273+19)*Q126)/(F125*K125*(Q125+U125/13.6))</f>
-        <v/>
+      <c r="AK121" s="1161" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122" ht="21.6" customHeight="1" s="730">
@@ -22436,9 +22364,8 @@
           <t>(</t>
         </is>
       </c>
-      <c r="L124" s="1876">
-        <f>(입력!D44-입력!D43)*1000</f>
-        <v/>
+      <c r="L124" s="1876" t="n">
+        <v>0</v>
       </c>
       <c r="M124" s="1827" t="n"/>
       <c r="N124" s="1827" t="n"/>
@@ -22466,9 +22393,8 @@
           <t>(</t>
         </is>
       </c>
-      <c r="F125" s="1890">
-        <f>'먼지측정 사전 Data'!R77</f>
-        <v/>
+      <c r="F125" s="1890" t="n">
+        <v>0.4019</v>
       </c>
       <c r="I125" s="807" t="inlineStr">
         <is>
@@ -22492,9 +22418,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q125" s="1032">
-        <f>'먼지측정 사전 Data'!H11</f>
-        <v/>
+      <c r="Q125" s="1032" t="n">
+        <v>751.7</v>
       </c>
       <c r="R125" s="1827" t="n"/>
       <c r="S125" s="1827" t="n"/>
@@ -22503,9 +22428,8 @@
           <t>+</t>
         </is>
       </c>
-      <c r="U125" s="1876">
-        <f>'먼지측정 사전 Data'!H83</f>
-        <v/>
+      <c r="U125" s="1876" t="n">
+        <v>29.79412960356355</v>
       </c>
       <c r="V125" s="1827" t="n"/>
       <c r="W125" s="1827" t="n"/>
@@ -22524,9 +22448,8 @@
           <t>273+</t>
         </is>
       </c>
-      <c r="M126" s="1160">
-        <f>'먼지측정 사전 Data'!R71</f>
-        <v/>
+      <c r="M126" s="1160" t="n">
+        <v>27.5</v>
       </c>
       <c r="Q126" s="1100" t="n">
         <v>760</v>
@@ -22597,9 +22520,8 @@
       <c r="Q128" s="1837" t="n"/>
       <c r="R128" s="1837" t="n"/>
       <c r="S128" s="1837" t="n"/>
-      <c r="T128" s="1889">
-        <f>J121*((21-'먼지측정 사전 Data'!R7)/(21-'먼지측정 사전 Data'!H7))</f>
-        <v/>
+      <c r="T128" s="1889" t="n">
+        <v>0</v>
       </c>
       <c r="U128" s="1837" t="n"/>
       <c r="V128" s="1837" t="n"/>
@@ -22630,9 +22552,8 @@
           <t>(</t>
         </is>
       </c>
-      <c r="Q130" s="1891">
-        <f>J121</f>
-        <v/>
+      <c r="Q130" s="1891" t="n">
+        <v>0</v>
       </c>
       <c r="T130" s="1044" t="inlineStr">
         <is>
@@ -22650,9 +22571,8 @@
         </is>
       </c>
       <c r="W130" s="1827" t="n"/>
-      <c r="X130" s="1032">
-        <f>'먼지측정 사전 Data'!R7</f>
-        <v/>
+      <c r="X130" s="1032" t="n">
+        <v>20.95</v>
       </c>
       <c r="Y130" s="1827" t="n"/>
       <c r="Z130" s="1827" t="n"/>
@@ -22686,9 +22606,8 @@
         </is>
       </c>
       <c r="W131" s="1829" t="n"/>
-      <c r="X131" s="1088">
-        <f>'먼지측정 사전 Data'!H7</f>
-        <v/>
+      <c r="X131" s="1088" t="n">
+        <v>20.95</v>
       </c>
       <c r="Y131" s="1829" t="n"/>
       <c r="Z131" s="1829" t="n"/>
@@ -22717,9 +22636,8 @@
       <c r="R132" s="1837" t="n"/>
       <c r="S132" s="1837" t="n"/>
       <c r="T132" s="1837" t="n"/>
-      <c r="U132" s="1889">
-        <f>J109/((21-'먼지측정 사전 Data'!R7)/(21-'먼지측정 사전 Data'!H7))</f>
-        <v/>
+      <c r="U132" s="1889" t="n">
+        <v>20766.79477132404</v>
       </c>
       <c r="V132" s="1837" t="n"/>
       <c r="W132" s="1837" t="n"/>
@@ -22735,9 +22653,8 @@
           <t>=</t>
         </is>
       </c>
-      <c r="AC132" s="1892">
-        <f>U132/60</f>
-        <v/>
+      <c r="AC132" s="1892" t="n">
+        <v>346.113246188734</v>
       </c>
       <c r="AD132" s="1837" t="n"/>
       <c r="AE132" s="1837" t="n"/>
@@ -22760,9 +22677,8 @@
           <t>(</t>
         </is>
       </c>
-      <c r="Q134" s="1893">
-        <f>J109</f>
-        <v/>
+      <c r="Q134" s="1893" t="n">
+        <v>20766.79477132404</v>
       </c>
       <c r="T134" s="1044" t="inlineStr">
         <is>
@@ -22780,9 +22696,8 @@
         </is>
       </c>
       <c r="W134" s="1827" t="n"/>
-      <c r="X134" s="1032">
-        <f>'먼지측정 사전 Data'!R7</f>
-        <v/>
+      <c r="X134" s="1032" t="n">
+        <v>20.95</v>
       </c>
       <c r="Y134" s="1827" t="n"/>
       <c r="Z134" s="1827" t="n"/>
@@ -22816,9 +22731,8 @@
         </is>
       </c>
       <c r="W135" s="1827" t="n"/>
-      <c r="X135" s="1032">
-        <f>'먼지측정 사전 Data'!H7</f>
-        <v/>
+      <c r="X135" s="1032" t="n">
+        <v>20.95</v>
       </c>
       <c r="Y135" s="1827" t="n"/>
       <c r="Z135" s="1827" t="n"/>
